--- a/Jobsheet 8/PWL_POS_5/public/template_user.xlsx
+++ b/Jobsheet 8/PWL_POS_5/public/template_user.xlsx
@@ -41,7 +41,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -55,6 +55,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -100,6 +108,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,13 +411,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.140625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -418,8 +427,9 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="5"/>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -430,7 +440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -443,5 +453,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>